--- a/artfynd/S 2980-2025 artfynd.xlsx
+++ b/artfynd/S 2980-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY120"/>
+  <dimension ref="A1:AZ120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108735</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16993802</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131895101</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/146843</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/146844</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1363,6 +1393,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/146845</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,6 +1514,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/146846</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1595,6 +1635,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/146856</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1697,6 +1742,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/147449</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1801,6 +1851,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6834730</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1923,6 +1978,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16496522</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2045,6 +2105,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16496546</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2157,6 +2222,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16993809</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2259,6 +2329,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53941602</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2375,6 +2450,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64198942</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2491,6 +2571,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64199538</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2607,6 +2692,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64199628</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2723,6 +2813,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202340</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2839,6 +2934,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202369</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2955,6 +3055,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202384</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3071,6 +3176,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202395</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3187,6 +3297,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202403</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3303,6 +3418,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202433</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3420,6 +3540,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67470310</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3539,6 +3664,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86295568</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3658,6 +3788,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86295574</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3762,6 +3897,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87428137</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3864,6 +4004,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109543230</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3979,6 +4124,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117689462</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4086,6 +4236,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120870134</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4197,6 +4352,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126708466</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4313,6 +4473,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116324</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4429,6 +4594,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121483</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4545,6 +4715,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125707</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4661,6 +4836,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64198938</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4777,6 +4957,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202362</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4893,6 +5078,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202405</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5011,6 +5201,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64416435</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5117,6 +5312,11 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81370632</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5232,6 +5432,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89718984</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5348,6 +5553,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103450518</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5463,6 +5673,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113307950</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5574,6 +5789,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120870132</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5673,6 +5893,11 @@
       <c r="AY45" t="inlineStr">
         <is>
           <t>Puggehatten, exkursion</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122450694</t>
         </is>
       </c>
     </row>
@@ -5777,6 +6002,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123704383</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5888,6 +6118,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126708397</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6004,6 +6239,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/153816</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6115,6 +6355,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/154457</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6231,6 +6476,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/154459</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6347,6 +6597,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/155045</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6463,6 +6718,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/155046</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6567,6 +6827,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6834736</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6679,6 +6944,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16998938</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6786,6 +7056,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53941603</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6902,6 +7177,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64198929</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7018,6 +7298,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64199658</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7134,6 +7419,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64199666</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7250,6 +7540,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202336</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7366,6 +7661,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202351</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7482,6 +7782,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202382</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7598,6 +7903,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202401</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7714,6 +8024,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202435</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7821,6 +8136,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64416434</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7940,6 +8260,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86295649</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8055,6 +8380,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86463747</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8157,6 +8487,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109543229</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8261,6 +8596,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6834737</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8377,6 +8717,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202397</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8492,6 +8837,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93986133</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8608,6 +8958,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/633653</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8724,6 +9079,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/633958</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8840,6 +9200,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/634125</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8947,6 +9312,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16999189</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9063,6 +9433,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64198965</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9179,6 +9554,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64199626</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9295,6 +9675,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202345</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9411,6 +9796,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202365</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9527,6 +9917,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202386</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9640,6 +10035,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16496592</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9758,6 +10158,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16496597</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9860,6 +10265,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121216613</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9962,6 +10372,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121216618</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10064,6 +10479,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121216619</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10166,6 +10586,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121360247</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10265,6 +10690,11 @@
       <c r="AY86" t="inlineStr">
         <is>
           <t>Puggehatten, exkursion</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122450699</t>
         </is>
       </c>
     </row>
@@ -10373,6 +10803,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123704396</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10482,6 +10917,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89724948</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10583,6 +11023,11 @@
           <t>Puggehatten, exkursion</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122450695</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10680,6 +11125,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117691153</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10777,6 +11227,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80656754</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10874,6 +11329,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85929311</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10989,6 +11449,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122090041</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11105,6 +11570,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64198940</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11221,6 +11691,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64200341</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11337,6 +11812,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64198935</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11443,6 +11923,11 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81370389</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11559,6 +12044,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202353</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11656,6 +12146,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89719299</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11753,6 +12248,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89719303</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11855,6 +12355,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93986216</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11962,6 +12467,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103450520</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12059,6 +12569,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117691151</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12161,6 +12676,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120870129</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12263,6 +12783,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120870156</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12365,6 +12890,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120870159</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12467,6 +12997,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123704402</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12578,6 +13113,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126708481</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12682,6 +13222,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6834734</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12789,6 +13334,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53941606</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12905,6 +13455,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64199651</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13021,6 +13576,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64200334</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13137,6 +13697,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202342</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13243,6 +13808,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78731946</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13349,6 +13919,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78731949</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13455,6 +14030,11 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81370263</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13569,6 +14149,11 @@
       <c r="AY117" t="inlineStr">
         <is>
           <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64202388</t>
         </is>
       </c>
     </row>
@@ -13678,6 +14263,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126708374</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13789,6 +14379,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127333979</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13901,8 +14496,134 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6282743</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>